--- a/rooms.xlsx
+++ b/rooms.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,6 +445,111 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>E-101</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>E-102</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>E-201</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>E-205</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>E-301</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Lab-1</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Laboratory</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Lab-2</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Laboratory</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rooms.xlsx
+++ b/rooms.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
